--- a/data/trans_dic/IP16A112_2023R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 54,23</t>
+          <t>25,38; 55,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 44,55</t>
+          <t>14,86; 44,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,64; 44,72</t>
+          <t>22,61; 42,64</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 53,55</t>
+          <t>22,81; 53,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,38; 57,37</t>
+          <t>35,5; 57,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,52; 52,66</t>
+          <t>34,68; 52,23</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 62,06</t>
+          <t>13,18; 61,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,21; 58,68</t>
+          <t>32,96; 60,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,59; 55,17</t>
+          <t>23,51; 55,6</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 61,13</t>
+          <t>31,89; 61,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 62,87</t>
+          <t>33,72; 63,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 57,45</t>
+          <t>37,36; 58,34</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,77; 49,62</t>
+          <t>24,25; 50,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,26; 50,85</t>
+          <t>37,85; 51,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 46,96</t>
+          <t>31,54; 47,59</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han consumido medicinas para el dolor y/o para bajar la fiebre (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10452</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7768</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18219</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6836; 14925</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4186; 12398</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12458; 23496</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18046</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29501</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47547</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10214; 24131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22655; 36805</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37656; 56717</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>28899</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26660</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10157; 47553</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18760; 34235</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31506; 74495</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16167</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30287</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9745; 18808</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11399; 21310</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24048; 37553</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>151613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43497; 90425</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>69163; 93943</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>114202; 172312</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A112_2023R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A112_2023R-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,38; 55,41</t>
+          <t>25,25; 55,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 44,02</t>
+          <t>15,69; 45,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 42,64</t>
+          <t>22,55; 44,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,81; 53,88</t>
+          <t>25,33; 54,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 57,68</t>
+          <t>34,31; 56,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,68; 52,23</t>
+          <t>33,85; 52,38</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 61,7</t>
+          <t>12,85; 62,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,96; 60,14</t>
+          <t>33,73; 60,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,51; 55,6</t>
+          <t>20,57; 55,37</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 61,54</t>
+          <t>31,66; 61,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,72; 63,03</t>
+          <t>32,84; 62,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,36; 58,34</t>
+          <t>36,57; 58,02</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,25; 50,42</t>
+          <t>25,01; 50,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,85; 51,42</t>
+          <t>37,19; 50,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,54; 47,59</t>
+          <t>32,59; 47,74</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6836; 14925</t>
+          <t>6803; 15000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4186; 12398</t>
+          <t>4419; 12806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12458; 23496</t>
+          <t>12425; 24263</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10214; 24131</t>
+          <t>11341; 24549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22655; 36805</t>
+          <t>21890; 36150</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37656; 56717</t>
+          <t>36753; 56884</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10157; 47553</t>
+          <t>9903; 48174</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18760; 34235</t>
+          <t>19199; 34248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31506; 74495</t>
+          <t>27563; 74195</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9745; 18808</t>
+          <t>9676; 18738</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11399; 21310</t>
+          <t>11104; 21095</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24048; 37553</t>
+          <t>23542; 37348</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43497; 90425</t>
+          <t>44851; 90132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69163; 93943</t>
+          <t>67953; 92577</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114202; 172312</t>
+          <t>118007; 172866</t>
         </is>
       </c>
     </row>
